--- a/fase_de_desarrollo/manual_carga_masiva_postura/Plantilla_SANTA_REYES_LEVANTE.xlsx
+++ b/fase_de_desarrollo/manual_carga_masiva_postura/Plantilla_SANTA_REYES_LEVANTE.xlsx
@@ -843,7 +843,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" sqref="J2:J1000" xr:uid="{6A365087-399B-418C-A374-7DE2C6A6E070}">
+    <dataValidation type="list" showErrorMessage="1" sqref="J2:J1000" xr:uid="{26E74012-CE81-4191-8916-F2E49E1199D4}">
       <formula1>"kg,qq"</formula1>
     </dataValidation>
   </dataValidations>
@@ -851,25 +851,25 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{56490543-028B-4AC3-BA41-63C71FC06487}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{FA75C3B9-285D-421A-93FD-5E4B00CDC1E3}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>K2:K1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{19DF8E6D-BC6F-4113-A943-3B77229A5051}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{30AF123C-7D39-433F-BF9B-9BD4AF6D5BAD}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>N2:N1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{1372C212-8D9C-4250-95FB-8A4CE2A38E0E}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{6A7905FF-6516-4C93-97C0-47C0968A7065}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>M2:M1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{0F922B15-CE6A-4F3B-AA2D-BDA2F1D97C5D}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{47734303-0A67-43BE-A564-5FF487A4F8D7}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
@@ -956,13 +956,13 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{647D4F86-33DF-4041-AA68-2453DFD0B366}">
+    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{03ADAF25-637B-46CF-B15C-59C743AACF47}">
       <formula1>"Ingreso,Traslado,Recepción,Consumo"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" sqref="E2:E1000" xr:uid="{D88FF09D-676A-4E3F-A549-702DCB7044E7}">
+    <dataValidation type="list" showErrorMessage="1" sqref="E2:E1000" xr:uid="{48C6D2BF-5474-4395-808B-20F04F93ABB1}">
       <formula1>"kg,qq"</formula1>
     </dataValidation>
-    <dataValidation type="list" showErrorMessage="1" sqref="N2:N1000" xr:uid="{B37F0AE1-6882-49E9-B7E0-39E55FC4F3D6}">
+    <dataValidation type="list" showErrorMessage="1" sqref="N2:N1000" xr:uid="{7519C479-0652-474D-A4C0-CC6EF6D27F80}">
       <formula1>"planta,bodega,granja"</formula1>
     </dataValidation>
   </dataValidations>
@@ -970,19 +970,19 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{058B242B-1016-4164-A591-6132BE47ADE7}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{98C96D99-748E-4956-9AD1-9A65E0A4C240}">
           <x14:formula1>
             <xm:f>Referencias!$A$2:$A$46</xm:f>
           </x14:formula1>
           <xm:sqref>C2:C1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{0EAC9D63-0176-4863-A13C-03E273B25A18}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{A3A93553-F658-416B-B0A4-5B5C1C215353}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I1000</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{82FF7296-04D5-4229-A21A-B59D05ACF345}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{5EDB731E-FA67-4415-96E3-50117A74ACA4}">
           <x14:formula1>
             <xm:f>Referencias!$L$2:$L$2</xm:f>
           </x14:formula1>
@@ -1037,7 +1037,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{052D2097-C45A-4FDE-B697-4EA0E87516F4}">
+    <dataValidation type="list" showErrorMessage="1" sqref="B2:B1000" xr:uid="{69D0B0BE-2563-4811-9EC0-AC9F9EC9921E}">
       <formula1>"Salida,Ingreso,Venta"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1045,7 +1045,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{48AC8229-EDD9-4420-AEDE-AF729D2C3440}">
+        <x14:dataValidation type="list" showErrorMessage="1" errorTitle="Valor inválido" error="Elegí un valor de la lista desplegable." xr:uid="{AEED09BD-44AC-41AE-AD26-3E6F1B38D36F}">
           <x14:formula1>
             <xm:f>Referencias!$H$2:$H$2</xm:f>
           </x14:formula1>
